--- a/Downloads/Splitflask-Financials/deliverables/SGM_2024_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/SGM_2024_Amendment_Packet.xlsx
@@ -221,7 +221,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -243,11 +243,18 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="004472C4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -454,6 +461,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1227,7 +1237,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Bank-classified: $6,368 (Meta/FB bank charges + PR + influencer). As-filed $6,901; $533 difference. TJ: confirm if additional ad spend exists on card ···1400 (see flagged item below).</t>
+          <t>Bank-classified: $6,368 (Meta/FB bank charges + PR + influencer). As-filed $6,901; $533 difference. TJ: confirm if additional ad spend exists on card ···1400 (see flagged item below). FIX 1: International Amazon ads MX/CA $703.99 added in Deductions tab (billed through MX/CA ad accounts, not in SGM US bank).</t>
         </is>
       </c>
     </row>
@@ -1277,10 +1287,10 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>189517</v>
+        <v>190220.99</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>189517</v>
+        <v>190220.99</v>
       </c>
       <c r="E30" s="7">
         <f> $36,000 + $30,241 + $9,528 + $6,368 + $107,380. Source: SGM_2024_Txns all 12 months footed. LAYER_5_COHERENCE_AUDIT.md.</f>
@@ -1651,7 +1661,7 @@
     </row>
     <row r="57" ht="6" customHeight="1"/>
     <row r="58">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="73" t="inlineStr">
         <is>
           <t>AMENDED ORDINARY INCOME / (LOSS)</t>
         </is>
@@ -1683,11 +1693,11 @@
         </is>
       </c>
       <c r="C60" s="26" t="n">
-        <v>-192339</v>
+        <v>-193042.99</v>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>LOCKED (CLAUDE.md Layer 6 + Path b). Revenue gross-up $102,772 PLUS sourced fee deductions $126,197 PLUS COGS correction $62,436 PLUS freight $65,918 PLUS opex correction $7,208 MINUS ending inventory reduction $57,600 = net −$192,339. Amendment is FAVORABLE — does NOT raise tax.</t>
+          <t>LOCKED (CLAUDE.md Layer 6 + Path b). Revenue gross-up $102,772 PLUS sourced fee deductions $126,197 PLUS COGS correction $62,436 PLUS freight $65,918 PLUS opex correction $7,208 MINUS ending inventory reduction $57,600 = net −$192,339. Amendment is FAVORABLE — does NOT raise tax. FIX 1: +intl ads −$703.99. Was -192339.0.</t>
         </is>
       </c>
     </row>
@@ -1698,11 +1708,11 @@
         </is>
       </c>
       <c r="D61" s="26" t="n">
-        <v>-249939</v>
+        <v>-250642.99</v>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Same as inventory method but no ending inventory deduction: adds $57,600 more expense. MORE favorable. TJ elects accounting method.</t>
+          <t>Same as inventory method but no ending inventory deduction: adds $57,600 more expense. MORE favorable. TJ elects accounting method. FIX 1: +intl ads −$703.99. Was -249939.0.</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3372,33 +3382,33 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other deductions (opex, bank fees, SaaS, CA tax, professional)</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n">
-        <v>107380</v>
-      </c>
-      <c r="C31" s="56" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>International Amazon ads (MX/CA, 2024 — billed in local currency)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>703.99</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>1120-S as-filed Other deductions preserved. Includes CA tax $4,360. Bank-classified categories: OPEX_SOFTWARE, BANK_FEES, PROF_SERVICES, etc.</t>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Splitflask-AMA Ad_Spend_2024.csv. MXN 1,138.82 × 0.0581 = $66.17 + CAD 865.54 × 0.7369 = $637.82. FX: 2024 avg IRS rates (MXN 17.21/USD; CAD 1.357/USD). NOT in US settlement — billed through MX/CA Amazon ad accounts. SGM owned the Amazon account in 2024. PURE EXPENSE per owner. FIX 1.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AmEx real business charges (patentYogi + podcast + domain)</t>
+          <t xml:space="preserve">  Other deductions (opex, bank fees, SaaS, CA tax, professional)</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>720</v>
+        <v>107380</v>
       </c>
       <c r="C32" s="56" t="inlineStr">
         <is>
@@ -3407,65 +3417,65 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>RECON_AMEX_2024: PatentYogi $152 + ALL IN Podcast $500 + IONOS/GoDaddy $68. Net-of-AmEx-payments correction. Move from OPEX_OTHER to OPEX_SOFTWARE.</t>
+          <t>1120-S as-filed Other deductions preserved. Includes CA tax $4,360. Bank-classified categories: OPEX_SOFTWARE, BANK_FEES, PROF_SERVICES, etc.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">  AmEx real business charges (patentYogi + podcast + domain)</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>720</v>
+      </c>
+      <c r="C33" s="56" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>RECON_AMEX_2024: PatentYogi $152 + ALL IN Podcast $500 + IONOS/GoDaddy $68. Net-of-AmEx-payments correction. Move from OPEX_OTHER to OPEX_SOFTWARE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="6" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
           <t>TOTAL OPERATING DEDUCTIONS (amended)</t>
         </is>
       </c>
-      <c r="B33" s="34" t="n">
+      <c r="B34" s="34" t="n">
         <v>189517</v>
       </c>
-      <c r="C33" s="56" t="inlineStr">
+      <c r="C34" s="56" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="D33" s="7">
+      <c r="D34" s="7">
         <f> $36K + $30,241 + $9,528 + $6,368 + $107,380 + $720 ≈ $190,237. LAYER_5_COHERENCE_AUDIT.md uses $189,517 (slight rounding diff). Corrected vs as-filed: +$7,208 (deeper, more favorable).</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>NON-DEDUCTIBLE — REMOVED FROM AMENDED RETURN</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>AmEx payments to personal 2021 balance — EXCLUDED</t>
-        </is>
-      </c>
-      <c r="B36" s="60" t="n">
-        <v>23676</v>
-      </c>
-      <c r="C36" s="61" t="inlineStr">
-        <is>
-          <t>EXCL</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>SGM paid Arize's personal AmEx debt from WF 8625 → owner draw. Non-deductible. RECON_AMEX_2024: all 7 months footed. Remove from deductions: −$23,676.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>Shopify Capital principal repayment — EXCLUDED</t>
+          <t>AmEx payments to personal 2021 balance — EXCLUDED</t>
         </is>
       </c>
       <c r="B37" s="60" t="n">
-        <v>37136</v>
+        <v>23676</v>
       </c>
       <c r="C37" s="61" t="inlineStr">
         <is>
@@ -3474,66 +3484,66 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>~$37K withheld from Shopify daily payouts = capital principal repayment. Non-deductible per owner decision (CLAUDE.md). TJ: pull Shopify Capital statement to isolate interest component.</t>
+          <t>SGM paid Arize's personal AmEx debt from WF 8625 → owner draw. Non-deductible. RECON_AMEX_2024: all 7 months footed. Remove from deductions: −$23,676.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="23" t="inlineStr">
         <is>
+          <t>Shopify Capital principal repayment — EXCLUDED</t>
+        </is>
+      </c>
+      <c r="B38" s="60" t="n">
+        <v>37136</v>
+      </c>
+      <c r="C38" s="61" t="inlineStr">
+        <is>
+          <t>EXCL</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>~$37K withheld from Shopify daily payouts = capital principal repayment. Non-deductible per owner decision (CLAUDE.md). TJ: pull Shopify Capital statement to isolate interest component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="6" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
           <t>SBA EIDL principal — EXCLUDED (interest only deductible)</t>
         </is>
       </c>
-      <c r="B38" s="60" t="n">
+      <c r="B39" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="61" t="inlineStr">
+      <c r="C39" s="61" t="inlineStr">
         <is>
           <t>TJ</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>TJ to split $13,320 total EIDL payment into principal (excl) + interest (incl). Current as-filed $9,528 interest may already be the interest-only portion.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="6" customHeight="1"/>
-    <row r="40">
-      <c r="A40" s="62" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="62" t="inlineStr">
         <is>
           <t>DEDUCTION TOTALS (Gross-Up Model)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  COGS (inventory method)</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n">
-        <v>332468</v>
-      </c>
-      <c r="C41" s="56" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>See COGS &amp; Inventory tab.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Operating deductions (bank-reconstructed)</t>
+          <t xml:space="preserve">  COGS (inventory method)</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>189517</v>
+        <v>332468</v>
       </c>
       <c r="C42" s="56" t="inlineStr">
         <is>
@@ -3542,18 +3552,18 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>See above.</t>
+          <t>See COGS &amp; Inventory tab.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Amazon fees + returns (sourced)</t>
+          <t xml:space="preserve">  Operating deductions (bank-reconstructed)</t>
         </is>
       </c>
       <c r="B43" s="9" t="n">
-        <v>74845</v>
+        <v>189517</v>
       </c>
       <c r="C43" s="56" t="inlineStr">
         <is>
@@ -3562,18 +3572,18 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>$52,007 + $22,838. Sourced from settlement CSV.</t>
+          <t>See above.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TikTok fees + shipping + ads (sourced)</t>
+          <t xml:space="preserve">  Amazon fees + returns (sourced)</t>
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>51352</v>
+        <v>74845</v>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
@@ -3582,18 +3592,18 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Sourced from quarterly income files.</t>
+          <t>$52,007 + $22,838. Sourced from settlement CSV.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Freight SGM net (sourced)</t>
+          <t xml:space="preserve">  TikTok fees + shipping + ads (sourced)</t>
         </is>
       </c>
       <c r="B45" s="9" t="n">
-        <v>65918</v>
+        <v>51352</v>
       </c>
       <c r="C45" s="56" t="inlineStr">
         <is>
@@ -3602,85 +3612,105 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>After intercompany reconciliation.</t>
+          <t>Sourced from quarterly income files.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Amazon MX/CA fees (ESTIMATE)</t>
+          <t xml:space="preserve">  Freight SGM net (sourced)</t>
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>26996</v>
-      </c>
-      <c r="C46" s="58" t="inlineStr">
-        <is>
-          <t>EST</t>
+        <v>65918</v>
+      </c>
+      <c r="C46" s="56" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Not yet sourced — TJ action item.</t>
+          <t>After intercompany reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Amazon MX/CA fees (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>26996</v>
+      </c>
+      <c r="C47" s="58" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Not yet sourced — TJ action item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Shopify Payments fee (ESTIMATE, Option B only)</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n">
+      <c r="B48" s="9" t="n">
         <v>5276</v>
       </c>
-      <c r="C47" s="58" t="inlineStr">
+      <c r="C48" s="58" t="inlineStr">
         <is>
           <t>EST</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Only if Shopify routes to SGM.</t>
         </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL DEDUCTIONS — sourced only</t>
-        </is>
-      </c>
-      <c r="B48" s="42" t="n">
-        <v>713100</v>
-      </c>
-      <c r="C48" s="56" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
-        </is>
-      </c>
-      <c r="D48" s="7">
-        <f> $332,468 + $189,517 + $74,845 + $51,352 + $65,918. Note: $332,468 + $189,517 + $74,845 + $51,352 + $65,918 = $714,100.</f>
-        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>TOTAL DEDUCTIONS — sourced only</t>
+        </is>
+      </c>
+      <c r="B49" s="42" t="n">
+        <v>713803.99</v>
+      </c>
+      <c r="C49" s="56" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D49" s="7">
+        <f> $332,468 + $189,517 + $74,845 + $51,352 + $65,918. Note: $332,468 + $189,517 + $74,845 + $51,352 + $65,918 = $714,100. FIX 1: +intl ads $703.99 (SGM, MX/CA 2024). Was $713100.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>TOTAL DEDUCTIONS — including estimates</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
-        <v>745372</v>
-      </c>
-      <c r="C49" s="58" t="inlineStr">
+      <c r="B50" s="29" t="n">
+        <v>746075.99</v>
+      </c>
+      <c r="C50" s="58" t="inlineStr">
         <is>
           <t>EST</t>
         </is>
       </c>
-      <c r="D49" s="7">
-        <f> sourced $714,100 + estimates $26,996 + $5,276. Deeper loss if confirmed.</f>
+      <c r="D50" s="7">
+        <f> sourced $714,100 + estimates $26,996 + $5,276. Deeper loss if confirmed. FIX 1: +intl ads $703.99. Was $745372.</f>
         <v/>
       </c>
     </row>
